--- a/02 Solution Architecture/Integration/EPMS_Integration_Matrix.xlsx
+++ b/02 Solution Architecture/Integration/EPMS_Integration_Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/02 Solution Architecture/Integration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24012FF7-C8E7-5A43-B78B-B5FBCD566C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53521999-2A08-774C-B3D0-C5F3E15007B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17940" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Integration Matrix" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>Jira</t>
   </si>
   <si>
-    <t>Project metadata (key, name)</t>
-  </si>
-  <si>
     <t>Bi-directional</t>
   </si>
   <si>
@@ -939,6 +936,9 @@
 -update ticket
 -fetch ticket
 -list/search tickets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project metadata </t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1379,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -1391,7 +1391,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -1399,25 +1399,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -1425,389 +1425,389 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="H6" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="H7" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="H9" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="H10" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="D11" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="H13" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="H15" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="D17" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="G17" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -1832,295 +1832,295 @@
     </row>
     <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B45" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B58" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B63" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B65" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B66" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2158,525 +2158,525 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>104</v>
-      </c>
       <c r="G2" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>122</v>
-      </c>
       <c r="D9" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>124</v>
-      </c>
       <c r="D10" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>126</v>
-      </c>
       <c r="D11" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>130</v>
-      </c>
       <c r="D13" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>136</v>
-      </c>
       <c r="D18" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>138</v>
-      </c>
       <c r="D19" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>140</v>
-      </c>
       <c r="D20" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="C21" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>143</v>
-      </c>
       <c r="D21" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>145</v>
-      </c>
       <c r="D22" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B23" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="D23" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="D24" s="10" t="s">
         <v>150</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>153</v>
-      </c>
       <c r="D25" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>155</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>157</v>
-      </c>
       <c r="D27" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="C28" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>160</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>162</v>
-      </c>
       <c r="D29" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="10" t="s">
+      <c r="D30" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B32" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>168</v>
-      </c>
       <c r="D32" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="C34" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>172</v>
-      </c>
       <c r="D34" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>174</v>
-      </c>
       <c r="D35" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2698,919 +2698,919 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" s="12" t="s">
         <v>100</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="C2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="G2" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>177</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>111</v>
-      </c>
       <c r="D5" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>114</v>
-      </c>
       <c r="D6" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="D7" s="12" t="s">
         <v>183</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>189</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>193</v>
-      </c>
       <c r="D13" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>195</v>
-      </c>
       <c r="D14" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>197</v>
-      </c>
       <c r="D15" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>199</v>
-      </c>
       <c r="D16" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>201</v>
-      </c>
       <c r="D17" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>202</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B22" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>208</v>
-      </c>
       <c r="D22" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B25" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="12" t="s">
-        <v>138</v>
-      </c>
       <c r="D25" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B26" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>140</v>
-      </c>
       <c r="D26" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="C27" s="12" t="s">
-        <v>212</v>
-      </c>
       <c r="D27" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C28" s="12" t="s">
-        <v>214</v>
-      </c>
       <c r="D28" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B29" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>216</v>
-      </c>
       <c r="D29" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>218</v>
-      </c>
       <c r="D30" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="C31" s="12" t="s">
-        <v>220</v>
-      </c>
       <c r="D31" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B32" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>222</v>
-      </c>
       <c r="D32" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B33" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>224</v>
-      </c>
       <c r="D33" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>226</v>
-      </c>
       <c r="D35" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B36" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>228</v>
-      </c>
       <c r="D36" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>142</v>
-      </c>
       <c r="C37" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="C40" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="D40" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B41" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>153</v>
-      </c>
       <c r="D41" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>155</v>
-      </c>
       <c r="D42" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B43" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>157</v>
-      </c>
       <c r="D43" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C44" s="12" t="s">
+      <c r="D44" s="12" t="s">
         <v>164</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B46" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="C46" s="12" t="s">
-        <v>168</v>
-      </c>
       <c r="D46" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B49" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>171</v>
-      </c>
       <c r="C49" s="12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B50" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>174</v>
-      </c>
       <c r="D50" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>236</v>
-      </c>
       <c r="D53" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B54" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>162</v>
-      </c>
       <c r="D54" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="C55" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C55" s="12" t="s">
-        <v>239</v>
-      </c>
       <c r="D55" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B56" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>241</v>
-      </c>
       <c r="D56" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B59" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>122</v>
-      </c>
       <c r="D59" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B60" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="D60" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B61" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="C61" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="D61" s="12" t="s">
         <v>245</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>248</v>
-      </c>
       <c r="D62" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B63" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C63" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>250</v>
-      </c>
       <c r="D63" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B64" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C64" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C64" s="12" t="s">
-        <v>252</v>
-      </c>
       <c r="D64" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -3628,47 +3628,47 @@
   <sheetData>
     <row r="2" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
     </row>
     <row r="4" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
     </row>
     <row r="5" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
     </row>
     <row r="6" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
     </row>
     <row r="7" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
@@ -3695,42 +3695,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">

--- a/02 Solution Architecture/Integration/EPMS_Integration_Matrix.xlsx
+++ b/02 Solution Architecture/Integration/EPMS_Integration_Matrix.xlsx
@@ -8,25 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sougatabagchi/Projects/MSIL/Enterprise-PM-Platform/epms-2/02 Solution Architecture/Integration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53521999-2A08-774C-B3D0-C5F3E15007B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76B7942-D19B-B040-B644-9C22263BE78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17940" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Integration Matrix" sheetId="1" r:id="rId1"/>
-    <sheet name="Fields to Capture in EPMP" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet7" sheetId="8" r:id="rId3"/>
+    <sheet name="JIRA KPI" sheetId="9" r:id="rId2"/>
+    <sheet name="Fields to Capture in EPMP" sheetId="2" r:id="rId3"/>
     <sheet name="JIRA Non Agile API" sheetId="4" r:id="rId4"/>
     <sheet name="JIRA  Agile API" sheetId="5" r:id="rId5"/>
     <sheet name="SAP Successfator API" sheetId="6" r:id="rId6"/>
     <sheet name="Zendesk API" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="343">
   <si>
     <t>System</t>
   </si>
@@ -940,14 +953,155 @@
   <si>
     <t xml:space="preserve">Project metadata </t>
   </si>
+  <si>
+    <t>KPI</t>
+  </si>
+  <si>
+    <t>Jira API</t>
+  </si>
+  <si>
+    <t>Fields to Fetch</t>
+  </si>
+  <si>
+    <t>JQL Example</t>
+  </si>
+  <si>
+    <t>Calculation in EPMS</t>
+  </si>
+  <si>
+    <t>Schedule Variance (Stage Level)</t>
+  </si>
+  <si>
+    <t>/rest/api/3/search, /issue/{id}</t>
+  </si>
+  <si>
+    <t>custom_start_date, duedate, resolutiondate, status, changelog</t>
+  </si>
+  <si>
+    <t>project = XYZ AND issuetype = Task AND status = Done</t>
+  </si>
+  <si>
+    <t>(Actual End Date - Planned End Date) / (Planned End Date - Planned Start Date)</t>
+  </si>
+  <si>
+    <t>On-time Delivery (Project Level)</t>
+  </si>
+  <si>
+    <t>/rest/api/3/search, /project/{key}/versions</t>
+  </si>
+  <si>
+    <t>duedate, resolutiondate, fixVersion, status</t>
+  </si>
+  <si>
+    <t>project = XYZ AND issuetype = Epic AND status = Done</t>
+  </si>
+  <si>
+    <t>IF(SV &gt; 0 → NO, ELSE YES)</t>
+  </si>
+  <si>
+    <t>On-time Delivery Variance (CoE Level)</t>
+  </si>
+  <si>
+    <t>/rest/api/3/search</t>
+  </si>
+  <si>
+    <t>duedate, resolutiondate, project, status</t>
+  </si>
+  <si>
+    <t>project in (A,B,C) AND status = Done AND resolutiondate &gt;= startOfMonth()</t>
+  </si>
+  <si>
+    <t>(Total Projects - Projects Completed On Time) / Total Planned Projects</t>
+  </si>
+  <si>
+    <t>Velocity Variance</t>
+  </si>
+  <si>
+    <t>/rest/agile/1.0/board/{boardId}/sprint, /board/{boardId}/issue</t>
+  </si>
+  <si>
+    <t>sprint, story_points, status</t>
+  </si>
+  <si>
+    <t>project = XYZ AND sprint = 123</t>
+  </si>
+  <si>
+    <t>(Story Points Delivered - Story Points Planned) / Story Points Planned</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
+  <si>
+    <t>/rest/api/3/search, /issue/{id}/worklog</t>
+  </si>
+  <si>
+    <t>story_points, timespent, worklog</t>
+  </si>
+  <si>
+    <t>project = XYZ AND issuetype in (Story, Task)</t>
+  </si>
+  <si>
+    <t>Size (Story Points) / Total Effort (Man-days)</t>
+  </si>
+  <si>
+    <t>Effort Variance</t>
+  </si>
+  <si>
+    <t>timeoriginalestimate, timespent, worklog</t>
+  </si>
+  <si>
+    <t>project = XYZ AND status = Done</t>
+  </si>
+  <si>
+    <t>(Actual Effort - Planned Effort) / Planned Effort</t>
+  </si>
+  <si>
+    <t>MSIL DRE</t>
+  </si>
+  <si>
+    <t>issuetype=Bug, custom_detected_by, environment, fixVersion</t>
+  </si>
+  <si>
+    <t>project = XYZ AND issuetype = Bug AND fixVersion = "Release1"</t>
+  </si>
+  <si>
+    <t>Defects caught by MSIL / (Defects caught by MSIL + Production defects)</t>
+  </si>
+  <si>
+    <t>Vendor DRE</t>
+  </si>
+  <si>
+    <t>issuetype=Bug, custom_defect_source, fixVersion, status</t>
+  </si>
+  <si>
+    <t>project = XYZ AND issuetype = Bug AND labels = vendor</t>
+  </si>
+  <si>
+    <t>Internal defects / (Internal + MSIL + Production defects)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -986,6 +1140,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="IBM Plex Sans"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="IBM Plex Sans"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1013,47 +1178,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1359,12 +1526,13 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="29.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="33" style="4" customWidth="1"/>
-    <col min="5" max="5" width="18.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="32.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="37.83203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.1640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" style="4" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1586,7 +1754,7 @@
       <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1612,7 +1780,7 @@
       <c r="C10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1638,7 +1806,7 @@
       <c r="C11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -1664,7 +1832,7 @@
       <c r="C12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1690,7 +1858,7 @@
       <c r="C13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -1716,7 +1884,7 @@
       <c r="C14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1742,7 +1910,7 @@
       <c r="C15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -1768,7 +1936,7 @@
       <c r="C16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -1794,7 +1962,7 @@
       <c r="C17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>282</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -1816,311 +1984,168 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7B7EF-3DF3-A14C-A6A9-4C7A6C6AB1F7}">
-  <dimension ref="A1:B66"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="28" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEFA71C6-EFD7-6E41-8098-FA310F86F535}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="9"/>
+    <col min="1" max="1" width="40.33203125" customWidth="1"/>
+    <col min="2" max="2" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="58.1640625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="12" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="12" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="12" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="12" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="12" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="12" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="12" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="12" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="12" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="12" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="12" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="12" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="12" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="12" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="12" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="12" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="12" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="12" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="12" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="12" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="12" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="12" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="12" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="12" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="12" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="12" t="s">
-        <v>81</v>
+    <row r="1" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -2129,14 +2154,312 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DEA26E4-B4BE-9B47-A781-38763DB2525F}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22A7B7EF-3DF3-A14C-A6A9-4C7A6C6AB1F7}">
+  <dimension ref="A1:B66"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="28" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="8"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+    <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="11" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="11" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="11" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="11" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="11" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="11" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="11" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="11" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="11" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2148,534 +2471,534 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="9"/>
-    <col min="5" max="5" width="34" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="9"/>
+    <col min="1" max="1" width="14" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="8"/>
+    <col min="5" max="5" width="34" style="8" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="D11" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="D12" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="D13" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="D14" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="D15" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="D16" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="D17" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="D18" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
+      <c r="D19" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
+      <c r="D20" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
+      <c r="D21" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+      <c r="D22" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
+      <c r="D23" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+    <row r="25" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
+    <row r="26" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
+    <row r="27" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
+    <row r="28" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
+      <c r="D28" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
+      <c r="D29" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
+    <row r="31" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
+    <row r="32" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="33" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="10" t="s">
+    <row r="33" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="34" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="10" t="s">
+    <row r="34" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="10" t="s">
+      <c r="D34" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="10" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10" t="s">
+      <c r="D35" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="9" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2689,927 +3012,927 @@
   <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" style="12"/>
-    <col min="2" max="2" width="20.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="16" style="12"/>
+    <col min="1" max="1" width="16" style="11"/>
+    <col min="2" max="2" width="20.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="16" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="12" t="s">
+      <c r="D18" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="11" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="12" t="s">
+      <c r="A44" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="12" t="s">
+      <c r="A54" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="11" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="11" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="11" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="11" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="11" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3620,63 +3943,46 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{570E7C8A-42CC-984F-8E6A-8B0D12002888}">
-  <dimension ref="A2:C9"/>
+  <dimension ref="A2:A8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="23" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="59" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-    </row>
-    <row r="4" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-    </row>
-    <row r="5" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-    </row>
-    <row r="6" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-    </row>
-    <row r="7" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-    </row>
-    <row r="8" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:1" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-    </row>
-    <row r="9" spans="1:3" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3688,37 +3994,37 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="33" style="9" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="9"/>
+    <col min="1" max="1" width="30.83203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="33" style="8" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>93</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -3726,7 +4032,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="96" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3734,58 +4040,58 @@
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="10"/>
+      <c r="A6" s="9"/>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="10"/>
+      <c r="A7" s="9"/>
     </row>
     <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="10"/>
+      <c r="A8" s="9"/>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="10"/>
+      <c r="A9" s="9"/>
     </row>
     <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
+      <c r="A10" s="9"/>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
+      <c r="A11" s="9"/>
     </row>
     <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="10"/>
+      <c r="A12" s="9"/>
     </row>
     <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
+      <c r="A13" s="9"/>
     </row>
     <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="10"/>
+      <c r="A14" s="9"/>
     </row>
     <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
+      <c r="A15" s="9"/>
     </row>
     <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="10"/>
+      <c r="A16" s="9"/>
     </row>
     <row r="17" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="10"/>
+      <c r="A17" s="9"/>
     </row>
     <row r="18" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
+      <c r="A18" s="9"/>
     </row>
     <row r="19" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
+      <c r="A19" s="9"/>
     </row>
     <row r="20" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
+      <c r="A20" s="9"/>
     </row>
     <row r="21" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
+      <c r="A21" s="9"/>
     </row>
     <row r="22" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
+      <c r="A22" s="9"/>
     </row>
     <row r="23" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="10"/>
+      <c r="A23" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
